--- a/Hoàng/2025/T5/TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA - CHI NHÁNH QUẢNG NAM (83-2025)/BÁO GIÁ, DANH SÁCH KSK - BẢO HIỂM ĐIỀU CHỈNH 2 final.xlsx
+++ b/Hoàng/2025/T5/TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA - CHI NHÁNH QUẢNG NAM (83-2025)/BÁO GIÁ, DANH SÁCH KSK - BẢO HIỂM ĐIỀU CHỈNH 2 final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA - CHI NHÁNH QUẢNG NAM (83-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2828A1-DDCF-410E-ACE0-9A0EE95B4321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46DA155-2D6D-4D73-8418-C1195EBD2018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG GÓI KHÁM" sheetId="11" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DANH SÁCH KHÁM THỰC TẾ'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'BÁO GIÁ'!$A$1:$G$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'BG GÓI KHÁM'!$A$1:$L$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BG GÓI KHÁM'!$A$1:$L$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'BÁO GIÁ'!#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BG GÓI KHÁM'!#REF!</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="124">
   <si>
     <t xml:space="preserve">CÔNG TY CỔ PHẦN BỆNH VIỆN THIỆN NHÂN ĐÀ NẴNG 
 Số 276-278-280 Đống Đa - P Thanh Bình -Thành Phố Đà Nẵng 
@@ -399,9 +399,6 @@
   </si>
   <si>
     <t>BỔ SUNG BẮT BUỘC</t>
-  </si>
-  <si>
-    <t>Có thể bỏ</t>
   </si>
   <si>
     <t>BỔ SUNG BẮT BUỘC (KẾT HỢP LDL-CHOLESTREOL + TRGLYCERID LÀ ĐƯỢC)</t>
@@ -582,7 +579,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,6 +613,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +877,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1106,53 +1115,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="6" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1166,6 +1128,60 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -1230,6 +1246,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1244,12 +1266,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1259,13 +1275,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1324,9 +1337,6 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1802,7 +1812,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="15" customWidth="1"/>
@@ -1823,73 +1833,73 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="111"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="114"/>
     </row>
     <row r="2" spans="1:17" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="114"/>
     </row>
     <row r="3" spans="1:17" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="114"/>
     </row>
     <row r="4" spans="1:17" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="111"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="114"/>
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="116"/>
+      <c r="L5" s="117"/>
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
@@ -1906,20 +1916,20 @@
       <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="116"/>
-      <c r="K7" s="116"/>
-      <c r="L7" s="117"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="120"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -1947,39 +1957,39 @@
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="120"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="123"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121" t="s">
+      <c r="A10" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="123"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="126"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -1987,18 +1997,18 @@
       <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="126"/>
+      <c r="A11" s="127"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="129"/>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
@@ -2006,181 +2016,183 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127" t="s">
+      <c r="C12" s="130"/>
+      <c r="D12" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="127" t="s">
+      <c r="E12" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="127" t="s">
+      <c r="F12" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="128" t="s">
+      <c r="G12" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="129" t="s">
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="132" t="s">
         <v>7</v>
       </c>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:17" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="127"/>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
+      <c r="A13" s="130"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
       <c r="G13" s="66" t="s">
         <v>74</v>
       </c>
       <c r="H13" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I13" s="16" t="s">
-        <v>122</v>
-      </c>
       <c r="J13" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="129"/>
+      <c r="L13" s="132"/>
       <c r="M13" s="47"/>
     </row>
     <row r="14" spans="1:17" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="130">
+      <c r="A14" s="135">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="132" t="s">
+      <c r="C14" s="137" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="133">
+      <c r="E14" s="138">
         <v>200000</v>
       </c>
-      <c r="F14" s="134">
+      <c r="F14" s="139">
         <f>MROUND(E14*95%,1000)</f>
         <v>190000</v>
       </c>
-      <c r="G14" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="K14" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="L14" s="135"/>
-      <c r="M14" s="70"/>
+      <c r="G14" s="138" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="138" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="138" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" s="138" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="138" t="s">
+        <v>75</v>
+      </c>
+      <c r="L14" s="133"/>
+      <c r="M14" s="70">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:17" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="130"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="132"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="137"/>
       <c r="D15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="133"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="135"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="133"/>
       <c r="M15" s="70"/>
     </row>
     <row r="16" spans="1:17" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="130"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="132"/>
+      <c r="A16" s="135"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="137"/>
       <c r="D16" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="133"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="133"/>
-      <c r="K16" s="133"/>
-      <c r="L16" s="135"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="133"/>
       <c r="M16" s="70"/>
     </row>
     <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="130"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="132"/>
+      <c r="A17" s="135"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="133"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="133"/>
-      <c r="J17" s="133"/>
-      <c r="K17" s="133"/>
-      <c r="L17" s="135"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="138"/>
+      <c r="L17" s="133"/>
       <c r="M17" s="18"/>
     </row>
     <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="130"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="132"/>
+      <c r="A18" s="135"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="137"/>
       <c r="D18" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="133"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
-      <c r="J18" s="133"/>
-      <c r="K18" s="133"/>
-      <c r="L18" s="135"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="138"/>
+      <c r="L18" s="133"/>
       <c r="M18" s="18"/>
     </row>
     <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="130"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="132"/>
+      <c r="A19" s="135"/>
+      <c r="B19" s="136"/>
+      <c r="C19" s="137"/>
       <c r="D19" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="133"/>
-      <c r="F19" s="134"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="133"/>
-      <c r="L19" s="135"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="138"/>
+      <c r="K19" s="138"/>
+      <c r="L19" s="133"/>
       <c r="M19" s="18"/>
     </row>
     <row r="20" spans="1:13" ht="33" x14ac:dyDescent="0.25">
@@ -2207,51 +2219,56 @@
       <c r="G20" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="63"/>
+      <c r="H20" s="93"/>
       <c r="I20" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="J20" s="63"/>
+      <c r="J20" s="93"/>
       <c r="K20" s="63" t="s">
         <v>75</v>
       </c>
       <c r="L20" s="50"/>
-      <c r="M20" s="18"/>
-    </row>
-    <row r="21" spans="1:13" s="93" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="88">
+      <c r="M20" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="100" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="94">
         <v>3</v>
       </c>
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="90" t="s">
+      <c r="C21" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="90" t="s">
+      <c r="D21" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="91">
+      <c r="E21" s="97">
         <v>59000</v>
       </c>
       <c r="F21" s="98">
         <f>MROUND(E21*95%,1000)</f>
         <v>56000</v>
       </c>
-      <c r="G21" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I21" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="J21" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="K21" s="101" t="s">
-        <v>75</v>
+      <c r="G21" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="J21" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="M21" s="18">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="66" x14ac:dyDescent="0.25">
@@ -2272,7 +2289,7 @@
         <v>75000</v>
       </c>
       <c r="F22" s="67">
-        <f t="shared" ref="F22:F39" si="0">MROUND(E22*95%,1000)</f>
+        <f t="shared" ref="F22:F37" si="0">MROUND(E22*95%,1000)</f>
         <v>71000</v>
       </c>
       <c r="G22" s="63" t="s">
@@ -2284,47 +2301,52 @@
       <c r="I22" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="63"/>
+      <c r="J22" s="93"/>
       <c r="K22" s="63" t="s">
         <v>75</v>
       </c>
       <c r="L22" s="50"/>
-      <c r="M22" s="18"/>
-    </row>
-    <row r="23" spans="1:13" s="93" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="88">
+      <c r="M22" s="18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="100" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="94">
         <v>5</v>
       </c>
-      <c r="B23" s="89" t="s">
+      <c r="B23" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="90" t="s">
+      <c r="C23" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="90" t="s">
+      <c r="D23" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="91">
+      <c r="E23" s="97">
         <v>27000</v>
       </c>
       <c r="F23" s="98">
         <f>MROUND(E23*95%,1000)</f>
         <v>26000</v>
       </c>
-      <c r="G23" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="J23" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="K23" s="101" t="s">
-        <v>75</v>
+      <c r="G23" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23" s="100">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -2332,7 +2354,7 @@
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
       </c>
-      <c r="B24" s="131" t="s">
+      <c r="B24" s="136" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -2341,10 +2363,10 @@
       <c r="D24" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="143">
+      <c r="E24" s="145">
         <v>60000</v>
       </c>
-      <c r="F24" s="134">
+      <c r="F24" s="139">
         <f t="shared" si="0"/>
         <v>57000</v>
       </c>
@@ -2357,29 +2379,31 @@
       <c r="I24" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="J24" s="63"/>
+      <c r="J24" s="93"/>
       <c r="K24" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="L24" s="144" t="s">
+      <c r="L24" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="M24" s="18"/>
+      <c r="M24" s="18">
+        <v>12</v>
+      </c>
     </row>
     <row r="25" spans="1:13" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="62">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
       </c>
-      <c r="B25" s="131"/>
+      <c r="B25" s="136"/>
       <c r="C25" s="23" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="143"/>
-      <c r="F25" s="134"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="139"/>
       <c r="G25" s="63" t="s">
         <v>75</v>
       </c>
@@ -2389,12 +2413,14 @@
       <c r="I25" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="63"/>
+      <c r="J25" s="93"/>
       <c r="K25" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="L25" s="144"/>
-      <c r="M25" s="18"/>
+      <c r="L25" s="146"/>
+      <c r="M25" s="18">
+        <v>12</v>
+      </c>
     </row>
     <row r="26" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="62">
@@ -2420,48 +2446,53 @@
       <c r="G26" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="63"/>
+      <c r="H26" s="93"/>
       <c r="I26" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="J26" s="63"/>
+      <c r="J26" s="93"/>
       <c r="K26" s="63" t="s">
         <v>75</v>
       </c>
       <c r="L26" s="50"/>
-      <c r="M26" s="18"/>
-    </row>
-    <row r="27" spans="1:13" s="93" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="88">
+      <c r="M26" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="100" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="94">
         <v>9</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="90" t="s">
+      <c r="B27" s="101"/>
+      <c r="C27" s="102" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="96" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="92" t="s">
+      <c r="E27" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="92" t="s">
+      <c r="F27" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="H27" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I27" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="J27" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" s="101" t="s">
-        <v>75</v>
+      <c r="G27" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="M27" s="100">
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -2499,7 +2530,9 @@
         <v>75</v>
       </c>
       <c r="L28" s="50"/>
-      <c r="M28" s="18"/>
+      <c r="M28" s="18">
+        <v>13</v>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62">
@@ -2529,7 +2562,9 @@
         <v>75</v>
       </c>
       <c r="L29" s="73"/>
-      <c r="M29" s="18"/>
+      <c r="M29" s="18">
+        <v>7</v>
+      </c>
     </row>
     <row r="30" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="62">
@@ -2564,211 +2599,230 @@
       <c r="J30" s="68"/>
       <c r="K30" s="68"/>
       <c r="L30" s="73"/>
-      <c r="M30" s="18"/>
-    </row>
-    <row r="31" spans="1:13" s="93" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A31" s="88">
+      <c r="M30" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="100" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A31" s="94">
         <v>11</v>
       </c>
-      <c r="B31" s="140" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="90" t="s">
+      <c r="B31" s="143" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="97" t="s">
+      <c r="D31" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="96">
+      <c r="E31" s="105">
         <v>41000</v>
       </c>
       <c r="F31" s="98">
         <f>MROUND(E31*95%,1000)</f>
         <v>39000</v>
       </c>
-      <c r="G31" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="H31" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I31" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="J31" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="K31" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="L31" s="99" t="s">
+      <c r="G31" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="I31" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="K31" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="106" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="62">
+      <c r="M31" s="100">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="100" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="107">
         <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
         <v>14</v>
       </c>
-      <c r="B32" s="141"/>
-      <c r="C32" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="65">
-        <v>41000</v>
-      </c>
-      <c r="F32" s="67">
+      <c r="B32" s="144"/>
+      <c r="C32" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="108" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="109">
+        <v>59000</v>
+      </c>
+      <c r="F32" s="98">
         <f t="shared" si="0"/>
-        <v>39000</v>
-      </c>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="73" t="s">
+        <v>56000</v>
+      </c>
+      <c r="G32" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="J32" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="K32" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="110" t="s">
         <v>117</v>
       </c>
-      <c r="M32" s="18"/>
-    </row>
-    <row r="33" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" s="111">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="66" x14ac:dyDescent="0.25">
       <c r="A33" s="62">
         <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
         <v>15</v>
       </c>
-      <c r="B33" s="141"/>
-      <c r="C33" s="90" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="102" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="103">
-        <v>59000</v>
-      </c>
-      <c r="F33" s="98">
+      <c r="B33" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="65">
+        <v>41000</v>
+      </c>
+      <c r="F33" s="67">
         <f t="shared" si="0"/>
-        <v>56000</v>
-      </c>
-      <c r="G33" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="H33" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I33" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="J33" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="K33" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="L33" s="100" t="s">
-        <v>118</v>
-      </c>
-      <c r="M33" s="18"/>
+        <v>39000</v>
+      </c>
+      <c r="G33" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="H33" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="J33" s="68"/>
+      <c r="K33" s="68"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="18">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="62">
         <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
         <v>16</v>
       </c>
-      <c r="B34" s="142"/>
+      <c r="B34" s="69" t="s">
+        <v>62</v>
+      </c>
       <c r="C34" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>58</v>
+        <v>63</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>64</v>
       </c>
       <c r="E34" s="65">
-        <v>59000</v>
+        <v>47000</v>
       </c>
       <c r="F34" s="67">
         <f t="shared" si="0"/>
-        <v>56000</v>
-      </c>
-      <c r="G34" s="63"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="63"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="73" t="s">
-        <v>117</v>
-      </c>
-      <c r="M34" s="18"/>
-    </row>
-    <row r="35" spans="1:13" ht="66" x14ac:dyDescent="0.25">
-      <c r="A35" s="62">
+        <v>45000</v>
+      </c>
+      <c r="G34" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" s="68"/>
+      <c r="I34" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="56" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A35" s="57">
         <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
         <v>17</v>
       </c>
-      <c r="B35" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="65">
-        <v>41000</v>
-      </c>
-      <c r="F35" s="67">
+      <c r="B35" s="74"/>
+      <c r="C35" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="60">
+        <v>121000</v>
+      </c>
+      <c r="F35" s="75">
         <f t="shared" si="0"/>
-        <v>39000</v>
-      </c>
-      <c r="G35" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="H35" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="I35" s="63" t="s">
-        <v>75</v>
-      </c>
+        <v>115000</v>
+      </c>
+      <c r="G35" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
       <c r="J35" s="68"/>
       <c r="K35" s="68"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="18"/>
-    </row>
-    <row r="36" spans="1:13" ht="33" x14ac:dyDescent="0.25">
-      <c r="A36" s="62">
+      <c r="L35" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="M35" s="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="56" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A36" s="57">
         <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
         <v>18</v>
       </c>
-      <c r="B36" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="65">
-        <v>47000</v>
-      </c>
-      <c r="F36" s="67">
+      <c r="B36" s="74"/>
+      <c r="C36" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="61">
+        <v>192000</v>
+      </c>
+      <c r="F36" s="75">
         <f t="shared" si="0"/>
-        <v>45000</v>
-      </c>
-      <c r="G36" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="H36" s="63"/>
-      <c r="I36" s="63" t="s">
-        <v>75</v>
-      </c>
+        <v>182000</v>
+      </c>
+      <c r="G36" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
       <c r="J36" s="68"/>
       <c r="K36" s="68"/>
-      <c r="L36" s="73"/>
-      <c r="M36" s="18"/>
+      <c r="L36" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="M36" s="55">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:13" s="56" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="57">
@@ -2777,17 +2831,17 @@
       </c>
       <c r="B37" s="74"/>
       <c r="C37" s="59" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="60">
-        <v>121000</v>
+        <v>70</v>
+      </c>
+      <c r="E37" s="61">
+        <v>173000</v>
       </c>
       <c r="F37" s="75">
         <f t="shared" si="0"/>
-        <v>115000</v>
+        <v>164000</v>
       </c>
       <c r="G37" s="76" t="s">
         <v>75</v>
@@ -2799,354 +2853,332 @@
       <c r="L37" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="M37" s="55"/>
-    </row>
-    <row r="38" spans="1:13" s="56" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="M37" s="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="57">
         <f>IF(LEN(C38)=0,"",COUNTA($C$14:C38))</f>
         <v>20</v>
       </c>
-      <c r="B38" s="74"/>
-      <c r="C38" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="61">
-        <v>192000</v>
+      <c r="B38" s="83"/>
+      <c r="C38" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="64">
+        <v>187000</v>
       </c>
       <c r="F38" s="75">
-        <f t="shared" si="0"/>
-        <v>182000</v>
-      </c>
-      <c r="G38" s="76" t="s">
-        <v>75</v>
-      </c>
+        <v>178000</v>
+      </c>
+      <c r="G38" s="68"/>
       <c r="H38" s="68"/>
       <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="77" t="s">
-        <v>77</v>
-      </c>
-      <c r="M38" s="55"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15">
+        <v>6</v>
+      </c>
     </row>
     <row r="39" spans="1:13" s="56" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="57">
         <f>IF(LEN(C39)=0,"",COUNTA($C$14:C39))</f>
         <v>21</v>
       </c>
-      <c r="B39" s="74"/>
-      <c r="C39" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>70</v>
+      <c r="B39" s="83"/>
+      <c r="C39" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="86" t="s">
+        <v>106</v>
       </c>
       <c r="E39" s="61">
-        <v>173000</v>
+        <v>231000</v>
       </c>
       <c r="F39" s="75">
-        <f t="shared" si="0"/>
-        <v>164000</v>
+        <v>220000</v>
       </c>
       <c r="G39" s="76" t="s">
         <v>75</v>
       </c>
       <c r="H39" s="68"/>
       <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
+      <c r="J39" s="93"/>
       <c r="K39" s="68"/>
       <c r="L39" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="M39" s="55"/>
-    </row>
-    <row r="40" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="82">
-        <f>IF(LEN(C40)=0,"",COUNTA($C$38:C40))</f>
-        <v>3</v>
-      </c>
+      <c r="M39" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="82"/>
       <c r="B40" s="83"/>
-      <c r="C40" s="84" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="84" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="64">
-        <v>187000</v>
-      </c>
-      <c r="F40" s="87">
-        <v>178000</v>
-      </c>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="22"/>
       <c r="G40" s="68"/>
       <c r="H40" s="68"/>
       <c r="I40" s="68"/>
-      <c r="J40" s="63"/>
-      <c r="K40" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="L40" s="15"/>
-    </row>
-    <row r="41" spans="1:13" s="56" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A41" s="82">
-        <f>IF(LEN(C41)=0,"",COUNTA($C$38:C41))</f>
-        <v>4</v>
-      </c>
-      <c r="B41" s="83"/>
-      <c r="C41" s="85" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" s="86" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" s="61">
-        <v>231000</v>
-      </c>
-      <c r="F41" s="87">
-        <v>220000</v>
-      </c>
-      <c r="G41" s="76" t="s">
-        <v>75</v>
-      </c>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="18"/>
+    </row>
+    <row r="41" spans="1:13" s="56" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="57"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="76"/>
       <c r="H41" s="68"/>
       <c r="I41" s="68"/>
       <c r="J41" s="68"/>
       <c r="K41" s="68"/>
-      <c r="L41" s="77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="82"/>
-      <c r="B42" s="83"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
-      <c r="I42" s="68"/>
-      <c r="J42" s="63"/>
-      <c r="K42" s="63"/>
-      <c r="L42" s="49"/>
+      <c r="L41" s="77"/>
+      <c r="M41" s="55"/>
+    </row>
+    <row r="42" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="130" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="130"/>
+      <c r="C42" s="130"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="78">
+        <f>SUMIF(G14:G39,"x",$F$14:$F$39)</f>
+        <v>1654000</v>
+      </c>
+      <c r="H42" s="78">
+        <f t="shared" ref="H42:K42" si="1">SUMIF(H14:H39,"x",$F$14:$F$39)</f>
+        <v>792000</v>
+      </c>
+      <c r="I42" s="78">
+        <f t="shared" si="1"/>
+        <v>973000</v>
+      </c>
+      <c r="J42" s="78">
+        <f t="shared" si="1"/>
+        <v>586000</v>
+      </c>
+      <c r="K42" s="78">
+        <f t="shared" si="1"/>
+        <v>1028000</v>
+      </c>
+      <c r="L42" s="26"/>
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:13" s="56" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="57"/>
-      <c r="B43" s="74"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="77"/>
-      <c r="M43" s="55"/>
-    </row>
-    <row r="44" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" s="127"/>
-      <c r="C44" s="127"/>
-      <c r="D44" s="127"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="66"/>
-      <c r="G44" s="78">
-        <f>SUMIF(G14:G41,"x",$F$14:$F$41)</f>
-        <v>1654000</v>
-      </c>
-      <c r="H44" s="78">
-        <f>SUMIF(H14:H39,"x",$F$14:$F$39)</f>
-        <v>792000</v>
-      </c>
-      <c r="I44" s="78">
-        <f>SUMIF(I14:I39,"x",$F$14:$F$39)</f>
-        <v>973000</v>
-      </c>
-      <c r="J44" s="78">
-        <f>SUMIF(J14:J40,"x",$F$14:$F$40)</f>
-        <v>586000</v>
-      </c>
-      <c r="K44" s="78">
-        <f>SUMIF(K14:K40,"x",$F$14:$F$40)</f>
-        <v>1028000</v>
-      </c>
-      <c r="L44" s="26"/>
-      <c r="M44" s="18"/>
-    </row>
-    <row r="45" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="30"/>
-    </row>
-    <row r="46" spans="1:13" s="43" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="39" t="s">
+    <row r="43" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="27"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="30"/>
+    </row>
+    <row r="44" spans="1:13" s="43" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="42"/>
-    </row>
-    <row r="47" spans="1:13" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="33"/>
-      <c r="B47" s="137" t="s">
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="42"/>
+    </row>
+    <row r="45" spans="1:13" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="33"/>
+      <c r="B45" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="137"/>
-      <c r="D47" s="137"/>
-      <c r="E47" s="137"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="137"/>
-      <c r="H47" s="137"/>
-      <c r="I47" s="137"/>
-      <c r="J47" s="137"/>
-      <c r="K47" s="137"/>
-      <c r="L47" s="137"/>
-    </row>
-    <row r="48" spans="1:13" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="33"/>
-      <c r="B48" s="137" t="s">
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="140"/>
+      <c r="I45" s="140"/>
+      <c r="J45" s="140"/>
+      <c r="K45" s="140"/>
+      <c r="L45" s="140"/>
+    </row>
+    <row r="46" spans="1:13" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="33"/>
+      <c r="B46" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="137"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
-      <c r="H48" s="137"/>
-      <c r="I48" s="137"/>
-      <c r="J48" s="137"/>
-      <c r="K48" s="137"/>
-      <c r="L48" s="137"/>
-    </row>
-    <row r="49" spans="1:12" s="35" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
-      <c r="B49" s="137" t="s">
+      <c r="C46" s="140"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="140"/>
+      <c r="I46" s="140"/>
+      <c r="J46" s="140"/>
+      <c r="K46" s="140"/>
+      <c r="L46" s="140"/>
+    </row>
+    <row r="47" spans="1:13" s="35" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="34"/>
+      <c r="B47" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="137"/>
-      <c r="I49" s="137"/>
-      <c r="J49" s="137"/>
-      <c r="K49" s="137"/>
-      <c r="L49" s="137"/>
-    </row>
-    <row r="50" spans="1:12" s="37" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
-      <c r="B50" s="136" t="s">
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="140"/>
+      <c r="K47" s="140"/>
+      <c r="L47" s="140"/>
+    </row>
+    <row r="48" spans="1:13" s="37" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="36"/>
+      <c r="B48" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="136"/>
-      <c r="D50" s="136"/>
-      <c r="E50" s="136"/>
-      <c r="F50" s="136"/>
-      <c r="G50" s="136"/>
-      <c r="H50" s="136"/>
-      <c r="I50" s="136"/>
-      <c r="J50" s="136"/>
-      <c r="K50" s="136"/>
-      <c r="L50" s="136"/>
-    </row>
-    <row r="51" spans="1:12" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="134"/>
+      <c r="D48" s="134"/>
+      <c r="E48" s="134"/>
+      <c r="F48" s="134"/>
+      <c r="G48" s="134"/>
+      <c r="H48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="134"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="134"/>
+    </row>
+    <row r="49" spans="1:12" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="31"/>
+      <c r="B49" s="140" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="140"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="140"/>
+      <c r="K49" s="140"/>
+      <c r="L49" s="140"/>
+    </row>
+    <row r="50" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="31"/>
+      <c r="B50" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="34"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="31"/>
-      <c r="B51" s="137" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" s="137"/>
-      <c r="D51" s="137"/>
-      <c r="E51" s="137"/>
-      <c r="F51" s="137"/>
-      <c r="G51" s="137"/>
-      <c r="H51" s="137"/>
-      <c r="I51" s="137"/>
-      <c r="J51" s="137"/>
-      <c r="K51" s="137"/>
-      <c r="L51" s="137"/>
-    </row>
-    <row r="52" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="31"/>
-      <c r="B52" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="5"/>
+      <c r="B51" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="34"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="1:12" s="43" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="41"/>
+      <c r="L52" s="42"/>
     </row>
     <row r="53" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="34"/>
+      <c r="B53" s="141" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="142" t="s">
+        <v>44</v>
+      </c>
       <c r="D53" s="38"/>
       <c r="E53" s="38"/>
       <c r="F53" s="38"/>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="1:12" s="43" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="42"/>
+    <row r="54" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31"/>
+      <c r="B54" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
-      <c r="B55" s="138" t="s">
-        <v>43</v>
-      </c>
-      <c r="C55" s="139" t="s">
-        <v>44</v>
-      </c>
+      <c r="B55" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="5"/>
       <c r="D55" s="38"/>
       <c r="E55" s="38"/>
       <c r="F55" s="38"/>
@@ -3157,49 +3189,17 @@
       <c r="K55" s="10"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="31"/>
-      <c r="B56" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="31"/>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="5"/>
-    </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B51:L51"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="B49:L49"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B45:L45"/>
     <mergeCell ref="H14:H19"/>
     <mergeCell ref="J14:J19"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="B49:L49"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B47:L47"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
@@ -3208,7 +3208,7 @@
     <mergeCell ref="I14:I19"/>
     <mergeCell ref="K14:K19"/>
     <mergeCell ref="L14:L19"/>
-    <mergeCell ref="B50:L50"/>
+    <mergeCell ref="B48:L48"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="B14:B19"/>
     <mergeCell ref="C14:C19"/>
@@ -3229,18 +3229,18 @@
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
+  <conditionalFormatting sqref="C44">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C1048576 C1:C11 C14:C45">
+  <conditionalFormatting sqref="C45:C1048576 C1:C11 C14:C43">
     <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C56:C1048576 C1:C11 C14:C45 C47:C54">
+  <conditionalFormatting sqref="C54:C1048576 C1:C11 C14:C43 C45:C52">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="12" max="163" man="1"/>
   </colBreaks>
@@ -3447,53 +3447,53 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="104">
+      <c r="A12" s="87">
         <v>11</v>
       </c>
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="104">
+      <c r="C12" s="87">
         <v>1976</v>
       </c>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="104" t="s">
+      <c r="E12" s="87" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="104">
+      <c r="A13" s="87">
         <v>12</v>
       </c>
-      <c r="B13" s="106" t="s">
+      <c r="B13" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="104">
+      <c r="C13" s="87">
         <v>1985</v>
       </c>
-      <c r="D13" s="104" t="s">
+      <c r="D13" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="E13" s="87" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="107">
+      <c r="A14" s="90">
         <v>13</v>
       </c>
-      <c r="B14" s="108" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="107">
+      <c r="B14" s="91" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="90">
         <v>1989</v>
       </c>
-      <c r="D14" s="107" t="s">
+      <c r="D14" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="104" t="s">
+      <c r="E14" s="87" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       <c r="D1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="162" t="s">
+      <c r="E1" s="92" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3733,48 +3733,48 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="111"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="114"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="114"/>
     </row>
     <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="114"/>
     </row>
     <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="111"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="117"/>
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
@@ -3786,15 +3786,15 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="117"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="120"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -3817,29 +3817,29 @@
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="120"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="123"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121" t="s">
+      <c r="A10" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="123"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="126"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -3847,13 +3847,13 @@
       <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="126"/>
+      <c r="A11" s="127"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="129"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
@@ -3861,120 +3861,120 @@
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127" t="s">
+      <c r="C12" s="130"/>
+      <c r="D12" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="128" t="s">
+      <c r="E12" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="128"/>
-      <c r="G12" s="129" t="s">
+      <c r="F12" s="131"/>
+      <c r="G12" s="132" t="s">
         <v>7</v>
       </c>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="127"/>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
+      <c r="A13" s="130"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
       <c r="E13" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="129"/>
+      <c r="G13" s="132"/>
       <c r="H13" s="47"/>
     </row>
     <row r="14" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="153">
+      <c r="A14" s="155">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="153" t="s">
+      <c r="B14" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="156" t="s">
+      <c r="C14" s="158" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="159">
+      <c r="E14" s="161">
         <v>200000</v>
       </c>
-      <c r="F14" s="159">
+      <c r="F14" s="161">
         <v>200000</v>
       </c>
-      <c r="G14" s="148"/>
+      <c r="G14" s="150"/>
       <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="155"/>
-      <c r="B15" s="155"/>
-      <c r="C15" s="157"/>
+      <c r="A15" s="157"/>
+      <c r="B15" s="157"/>
+      <c r="C15" s="159"/>
       <c r="D15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="160"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="149"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="151"/>
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="157"/>
+      <c r="A16" s="157"/>
+      <c r="B16" s="157"/>
+      <c r="C16" s="159"/>
       <c r="D16" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="160"/>
-      <c r="F16" s="160"/>
-      <c r="G16" s="149"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="151"/>
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="157"/>
+      <c r="A17" s="157"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="159"/>
       <c r="D17" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="160"/>
-      <c r="F17" s="160"/>
-      <c r="G17" s="149"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="151"/>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="155"/>
-      <c r="B18" s="155"/>
-      <c r="C18" s="157"/>
+      <c r="A18" s="157"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="160"/>
-      <c r="F18" s="160"/>
-      <c r="G18" s="149"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="151"/>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="154"/>
-      <c r="B19" s="154"/>
-      <c r="C19" s="158"/>
+      <c r="A19" s="156"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="160"/>
       <c r="D19" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="161"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="150"/>
+      <c r="E19" s="163"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="152"/>
       <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.25">
@@ -4028,7 +4028,7 @@
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
       </c>
-      <c r="B22" s="130" t="s">
+      <c r="B22" s="135" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="23" t="s">
@@ -4037,13 +4037,13 @@
       <c r="D22" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="151">
+      <c r="E22" s="153">
         <v>60000</v>
       </c>
-      <c r="F22" s="151">
+      <c r="F22" s="153">
         <v>60000</v>
       </c>
-      <c r="G22" s="153" t="s">
+      <c r="G22" s="155" t="s">
         <v>25</v>
       </c>
       <c r="H22" s="18"/>
@@ -4053,16 +4053,16 @@
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
       </c>
-      <c r="B23" s="130"/>
+      <c r="B23" s="135"/>
       <c r="C23" s="23" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="154"/>
+      <c r="E23" s="154"/>
+      <c r="F23" s="154"/>
+      <c r="G23" s="156"/>
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
@@ -4318,12 +4318,12 @@
       <c r="H36" s="18"/>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="145" t="s">
+      <c r="A37" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="146"/>
-      <c r="C37" s="146"/>
-      <c r="D37" s="147"/>
+      <c r="B37" s="148"/>
+      <c r="C37" s="148"/>
+      <c r="D37" s="149"/>
       <c r="E37" s="16">
         <f>SUM(E14:E32)</f>
         <v>996000</v>
@@ -4357,58 +4357,58 @@
     </row>
     <row r="40" spans="1:8" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="33"/>
-      <c r="B40" s="137" t="s">
+      <c r="B40" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="137"/>
-      <c r="D40" s="137"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
     </row>
     <row r="41" spans="1:8" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="33"/>
-      <c r="B41" s="137" t="s">
+      <c r="B41" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="137"/>
-      <c r="D41" s="137"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
     </row>
     <row r="42" spans="1:8" s="35" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="34"/>
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
     </row>
     <row r="43" spans="1:8" s="37" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="36"/>
-      <c r="B43" s="136" t="s">
+      <c r="B43" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="136"/>
-      <c r="D43" s="136"/>
-      <c r="E43" s="136"/>
-      <c r="F43" s="136"/>
-      <c r="G43" s="136"/>
+      <c r="C43" s="134"/>
+      <c r="D43" s="134"/>
+      <c r="E43" s="134"/>
+      <c r="F43" s="134"/>
+      <c r="G43" s="134"/>
     </row>
     <row r="44" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="31"/>
-      <c r="B44" s="137" t="s">
+      <c r="B44" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="137"/>
-      <c r="D44" s="137"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
+      <c r="C44" s="140"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
     </row>
     <row r="45" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="31"/>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="48" spans="1:8" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="31"/>
-      <c r="B48" s="138" t="s">
+      <c r="B48" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="139" t="s">
+      <c r="C48" s="142" t="s">
         <v>44</v>
       </c>
       <c r="D48" s="38"/>
